--- a/Use_cases/Use_case_2-Bo_et_al_2011.xlsx
+++ b/Use_cases/Use_case_2-Bo_et_al_2011.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\Case_studies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\Use_cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B8160C-3CB5-4C0F-B92D-507E4ECCCB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D480ED2-450D-4868-BFB5-8AA2DD7C6958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C772E4A6-6938-4714-B988-E5854FC383F1}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{C772E4A6-6938-4714-B988-E5854FC383F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Full" sheetId="8" r:id="rId1"/>
@@ -2763,7 +2763,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2864,12 +2864,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -3426,7 +3420,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B7A37C-4894-4CC6-96F9-8A445DB3D3C0}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q165"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3502,7 +3495,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>174</v>
       </c>
@@ -3537,7 +3530,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>174</v>
       </c>
@@ -3572,7 +3565,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>174</v>
       </c>
@@ -3602,7 +3595,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>174</v>
       </c>
@@ -3634,7 +3627,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>174</v>
       </c>
@@ -3666,7 +3659,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>174</v>
       </c>
@@ -3698,7 +3691,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>174</v>
       </c>
@@ -3728,7 +3721,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>174</v>
       </c>
@@ -3760,7 +3753,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>174</v>
       </c>
@@ -3792,7 +3785,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>174</v>
       </c>
@@ -3824,7 +3817,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>174</v>
       </c>
@@ -3856,7 +3849,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>174</v>
       </c>
@@ -3891,7 +3884,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>174</v>
       </c>
@@ -3926,7 +3919,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>174</v>
       </c>
@@ -3961,7 +3954,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>174</v>
       </c>
@@ -3991,7 +3984,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>254</v>
       </c>
@@ -4029,7 +4022,7 @@
         <v>10.907166999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>254</v>
       </c>
@@ -4067,7 +4060,7 @@
         <v>41.107500000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>254</v>
       </c>
@@ -4102,7 +4095,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>254</v>
       </c>
@@ -4137,7 +4130,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>254</v>
       </c>
@@ -4175,7 +4168,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>254</v>
       </c>
@@ -4213,7 +4206,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="17"/>
       <c r="C23" s="13" t="s">
         <v>86</v>
@@ -4240,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B24" s="17"/>
       <c r="C24" s="13" t="s">
         <v>87</v>
@@ -4264,7 +4257,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B25" s="17"/>
       <c r="C25" s="13" t="s">
         <v>88</v>
@@ -4286,7 +4279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B26" s="17"/>
       <c r="C26" s="13" t="s">
         <v>89</v>
@@ -4308,7 +4301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="108" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="17"/>
       <c r="C27" s="13" t="s">
         <v>90</v>
@@ -4480,7 +4473,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="B34" s="17" t="s">
         <v>255</v>
       </c>
@@ -4916,7 +4909,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="85.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="17" t="s">
         <v>369</v>
       </c>
@@ -4951,7 +4944,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="84.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" ht="84.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="17" t="s">
         <v>369</v>
       </c>
@@ -4986,7 +4979,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" ht="72" x14ac:dyDescent="0.3">
       <c r="B52" s="17" t="s">
         <v>369</v>
       </c>
@@ -5018,7 +5011,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="17" t="s">
         <v>369</v>
       </c>
@@ -5050,7 +5043,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B54" s="17" t="s">
         <v>369</v>
       </c>
@@ -5077,7 +5070,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B55" s="21" t="s">
         <v>391</v>
       </c>
@@ -5127,7 +5120,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B57" s="21" t="s">
         <v>391</v>
       </c>
@@ -5210,7 +5203,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" spans="2:16" ht="130.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="21" t="s">
         <v>391</v>
       </c>
@@ -5234,7 +5227,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="2:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B61" s="21" t="s">
         <v>391</v>
       </c>
@@ -5258,7 +5251,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="2:16" ht="291.60000000000002" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" ht="291.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="21" t="s">
         <v>391</v>
       </c>
@@ -5293,7 +5286,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="63" spans="2:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B63" s="21" t="s">
         <v>391</v>
       </c>
@@ -5325,7 +5318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="21" t="s">
         <v>391</v>
       </c>
@@ -5357,7 +5350,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B65" s="21" t="s">
         <v>391</v>
       </c>
@@ -5386,7 +5379,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" ht="144" x14ac:dyDescent="0.3">
       <c r="B66" s="21" t="s">
         <v>391</v>
       </c>
@@ -5418,7 +5411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="187.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B67" s="21" t="s">
         <v>391</v>
       </c>
@@ -5447,7 +5440,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B68" s="21" t="s">
         <v>391</v>
       </c>
@@ -5479,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="B69" s="21" t="s">
         <v>391</v>
       </c>
@@ -5511,7 +5504,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="B70" s="21" t="s">
         <v>391</v>
       </c>
@@ -5537,7 +5530,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B71" s="21" t="s">
         <v>391</v>
       </c>
@@ -5563,7 +5556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B72" s="21" t="s">
         <v>391</v>
       </c>
@@ -5595,7 +5588,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B73" s="21" t="s">
         <v>391</v>
       </c>
@@ -5627,7 +5620,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="B74" s="21" t="s">
         <v>391</v>
       </c>
@@ -5659,7 +5652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B75" s="21" t="s">
         <v>391</v>
       </c>
@@ -5685,7 +5678,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B76" s="21" t="s">
         <v>391</v>
       </c>
@@ -5711,7 +5704,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="74.400000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="21" t="s">
         <v>391</v>
       </c>
@@ -5743,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="172.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="21" t="s">
         <v>391</v>
       </c>
@@ -5775,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B79" s="21" t="s">
         <v>391</v>
       </c>
@@ -5921,7 +5914,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B84" s="23" t="s">
         <v>468</v>
       </c>
@@ -6046,7 +6039,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
         <v>467</v>
       </c>
@@ -6436,7 +6429,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="54.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
         <v>467</v>
       </c>
@@ -6471,7 +6464,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A102" s="11" t="s">
         <v>467</v>
       </c>
@@ -6509,7 +6502,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A103" s="11" t="s">
         <v>467</v>
       </c>
@@ -6544,7 +6537,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
         <v>467</v>
       </c>
@@ -6582,7 +6575,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="11" t="s">
         <v>467</v>
       </c>
@@ -6617,7 +6610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
         <v>467</v>
       </c>
@@ -6646,7 +6639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="11" t="s">
         <v>467</v>
       </c>
@@ -6681,7 +6674,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="11" t="s">
         <v>467</v>
       </c>
@@ -6713,7 +6706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
         <v>467</v>
       </c>
@@ -6742,7 +6735,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="11" t="s">
         <v>467</v>
       </c>
@@ -6778,7 +6771,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>467</v>
       </c>
@@ -6834,7 +6827,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="11" t="s">
         <v>467</v>
       </c>
@@ -6861,7 +6854,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
         <v>467</v>
       </c>
@@ -6894,7 +6887,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A115" s="11" t="s">
         <v>467</v>
       </c>
@@ -6926,7 +6919,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
         <v>467</v>
       </c>
@@ -6958,7 +6951,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A117" s="11" t="s">
         <v>467</v>
       </c>
@@ -6988,7 +6981,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="11" t="s">
         <v>467</v>
       </c>
@@ -7017,7 +7010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A119" s="11" t="s">
         <v>467</v>
       </c>
@@ -7049,7 +7042,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A120" s="11" t="s">
         <v>467</v>
       </c>
@@ -7078,7 +7071,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A121" s="11" t="s">
         <v>467</v>
       </c>
@@ -7107,7 +7100,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>467</v>
       </c>
@@ -7134,7 +7127,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="11" t="s">
         <v>467</v>
       </c>
@@ -7163,7 +7156,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="113.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" ht="113.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="11" t="s">
         <v>467</v>
       </c>
@@ -7303,7 +7296,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="129" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A129" s="11" t="s">
         <v>467</v>
       </c>
@@ -7335,7 +7328,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
         <v>467</v>
       </c>
@@ -7616,7 +7609,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="140" spans="1:16" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A140" s="11" t="s">
         <v>467</v>
       </c>
@@ -7846,7 +7839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="148" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A148" s="11" t="s">
         <v>254</v>
       </c>
@@ -7878,7 +7871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A149" s="11" t="s">
         <v>254</v>
       </c>
@@ -7904,7 +7897,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" s="11" t="s">
         <v>254</v>
       </c>
@@ -7927,7 +7920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="11" t="s">
         <v>254</v>
       </c>
@@ -7947,7 +7940,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B152" s="17" t="s">
         <v>668</v>
       </c>
@@ -7974,7 +7967,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="11" t="s">
         <v>254</v>
       </c>
@@ -7993,7 +7986,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="11" t="s">
         <v>254</v>
       </c>
@@ -8013,7 +8006,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="11" t="s">
         <v>254</v>
       </c>
@@ -8033,7 +8026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="11" t="s">
         <v>254</v>
       </c>
@@ -8056,7 +8049,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="11" t="s">
         <v>254</v>
       </c>
@@ -8076,7 +8069,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="11" t="s">
         <v>254</v>
       </c>
@@ -8096,7 +8089,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" s="11" t="s">
         <v>254</v>
       </c>
@@ -8122,7 +8115,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="11" t="s">
         <v>254</v>
       </c>
@@ -8142,7 +8135,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="161" spans="1:16" s="34" customFormat="1" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" s="34" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A161" s="28" t="s">
         <v>254</v>
       </c>
@@ -8306,83 +8299,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q165" xr:uid="{D65FE3B8-EA9F-4A1C-8B4E-F3566D1718E8}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="asmr:analyzedAreaUnit"/>
-        <filter val="asmr:analyzedAreaValue"/>
-        <filter val="asmr:analyzedTime"/>
-        <filter val="asmr:armLength"/>
-        <filter val="asmr:bait"/>
-        <filter val="asmr:baitQuantity"/>
-        <filter val="asmr:batterySystem"/>
-        <filter val="asmr:cameraSystem"/>
-        <filter val="asmr:canisterModel"/>
-        <filter val="asmr:costAnalysisCurrency"/>
-        <filter val="asmr:costAnalysisUnit"/>
-        <filter val="asmr:costPerCostAnalysisUnit"/>
-        <filter val="asmr:divingGasMix"/>
-        <filter val="asmr:ecologicalParameters"/>
-        <filter val="asmr:ecoregionCode"/>
-        <filter val="asmr:ecoregionName"/>
-        <filter val="asmr:ecoregionScheme"/>
-        <filter val="asmr:equipmentCostPerUnit"/>
-        <filter val="asmr:excludedSamplingEffortUnit"/>
-        <filter val="asmr:excludedSamplingEffortUnitRationale"/>
-        <filter val="asmr:excludedSubstrateScope"/>
-        <filter val="asmr:exSituAbioticParametersAnalyzed"/>
-        <filter val="asmr:fieldOfView"/>
-        <filter val="asmr:geomorphologicalContext"/>
-        <filter val="asmr:geomorphologyClassificationScheme"/>
-        <filter val="asmr:habitatClassificationScheme"/>
-        <filter val="asmr:inSituAbioticlParametersAnalyzed"/>
-        <filter val="asmr:inSituAbioticParametersCollected"/>
-        <filter val="asmr:lightSystem"/>
-        <filter val="asmr:manipulatorArms"/>
-        <filter val="asmr:maximumAnalyzedDepth"/>
-        <filter val="asmr:maximumSurveyedDepth"/>
-        <filter val="asmr:minimumAnalyzedDepth"/>
-        <filter val="asmr:minimumSurveyedDepth"/>
-        <filter val="asmr:navigationSpeed"/>
-        <filter val="asmr:otherFaunaAttraction"/>
-        <filter val="asmr:pelagicORbenthicBaitedPlatform"/>
-        <filter val="asmr:personnelCostPerUnit"/>
-        <filter val="asmr:physiographicContext"/>
-        <filter val="asmr:positioningSystem"/>
-        <filter val="asmr:protectedAreaOrOECM"/>
-        <filter val="asmr:protocolPreventionMeasures"/>
-        <filter val="asmr:protocolRisks"/>
-        <filter val="asmr:sampleContainer"/>
-        <filter val="asmr:samplingPlatform"/>
-        <filter val="asmr:samplingPlatformModel"/>
-        <filter val="asmr:sensors"/>
-        <filter val="asmr:sensorsCalibration"/>
-        <filter val="asmr:sizeReferenceSystem"/>
-        <filter val="asmr:spatialReplicates"/>
-        <filter val="asmr:standardFaciesValue"/>
-        <filter val="asmr:standardGeographicFeatureClassification"/>
-        <filter val="asmr:standardGeographicFeatureValue"/>
-        <filter val="asmr:standardHabitatValue"/>
-        <filter val="asmr:standardSubstrateClass"/>
-        <filter val="asmr:standardSubstrateGroup"/>
-        <filter val="asmr:standardSubstrateOrigin"/>
-        <filter val="asmr:standardSubstrateSubclass"/>
-        <filter val="asmr:standardTargetHabitatScope"/>
-        <filter val="asmr:substrateClassificationScheme"/>
-        <filter val="asmr:substrateScope"/>
-        <filter val="asmr:surveyedTime"/>
-        <filter val="asmr:surveyType"/>
-        <filter val="asmr:temporalReplicates"/>
-        <filter val="asmr:temporalScale"/>
-        <filter val="asmr:validationProtocolDescription"/>
-        <filter val="asmr:verbatimGeomorphologicalContext"/>
-        <filter val="asmr:verbatimHabitat"/>
-        <filter val="asmr:verbatimLithology"/>
-        <filter val="asmr:verbatimProtectionMeasures"/>
-        <filter val="asmr:verbatimSubstrate"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q165" xr:uid="{D65FE3B8-EA9F-4A1C-8B4E-F3566D1718E8}"/>
   <hyperlinks>
     <hyperlink ref="N10" r:id="rId1" xr:uid="{FE7BA7A2-708B-4BF5-AAC4-9AA8C158A135}"/>
     <hyperlink ref="L16" r:id="rId2" xr:uid="{1D7C098B-C020-483C-9C6A-B8831B2E8513}"/>
